--- a/questionnaire_templates/035_human_system_pressure_assessment--questionnaire_templates.xlsx
+++ b/questionnaire_templates/035_human_system_pressure_assessment--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -780,8 +780,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -809,12 +809,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'very_good'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Very good'}</t>
+          <t>Very good</t>
         </is>
       </c>
     </row>
@@ -826,12 +826,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_good'}</t>
+          <t>somewhat_good</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat good'}</t>
+          <t>Somewhat good</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'not_very_good'}</t>
+          <t>not_very_good</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Not very good'}</t>
+          <t>Not very good</t>
         </is>
       </c>
     </row>
@@ -860,12 +860,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'very_bad'}</t>
+          <t>very_bad</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Very bad'}</t>
+          <t>Very bad</t>
         </is>
       </c>
     </row>
@@ -877,12 +877,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'1-5_years'}</t>
+          <t>1-5_years</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': '1-5 years'}</t>
+          <t>1-5 years</t>
         </is>
       </c>
     </row>
@@ -894,12 +894,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'5-10_years'}</t>
+          <t>5-10_years</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': '5-10 years'}</t>
+          <t>5-10 years</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'10+_years'}</t>
+          <t>10+_years</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': '10+ years'}</t>
+          <t>10+ years</t>
         </is>
       </c>
     </row>
@@ -928,12 +928,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'ceo'}</t>
+          <t>ceo</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'CEO'}</t>
+          <t>CEO</t>
         </is>
       </c>
     </row>
@@ -945,12 +945,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Manager'}</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -962,12 +962,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'employee'}</t>
+          <t>employee</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Employee'}</t>
+          <t>Employee</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'lack_of_work-life_balance'}</t>
+          <t>lack_of_work-life_balance</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Lack of work-life balance'}</t>
+          <t>Lack of work-life balance</t>
         </is>
       </c>
     </row>
@@ -996,12 +996,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'lack_of_recognition'}</t>
+          <t>lack_of_recognition</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Lack of recognition'}</t>
+          <t>Lack of recognition</t>
         </is>
       </c>
     </row>
@@ -1013,12 +1013,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'conflict_with_colleagues'}</t>
+          <t>conflict_with_colleagues</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Conflict with colleagues'}</t>
+          <t>Conflict with colleagues</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'poor_communication'}</t>
+          <t>poor_communication</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Poor communication'}</t>
+          <t>Poor communication</t>
         </is>
       </c>
     </row>
@@ -1047,12 +1047,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'mental_health_support'}</t>
+          <t>mental_health_support</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Mental health support'}</t>
+          <t>Mental health support</t>
         </is>
       </c>
     </row>
@@ -1064,12 +1064,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'financial_support'}</t>
+          <t>financial_support</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Financial support'}</t>
+          <t>Financial support</t>
         </is>
       </c>
     </row>
@@ -1081,12 +1081,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'career_development'}</t>
+          <t>career_development</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Career development'}</t>
+          <t>Career development</t>
         </is>
       </c>
     </row>
